--- a/KNK업무시스템구축_엑셀/V2/02_자동화_완제품/KNK_자동화_완제품_베트남_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V2/02_자동화_완제품/KNK_자동화_완제품_베트남_입력_2026.xlsx
@@ -1342,7 +1342,7 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>M-260105-4</t>
+          <t>M-260105-3</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>M-260105-5</t>
+          <t>M-260105-4</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>M-260105-6</t>
+          <t>M-260105-5</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>M-260105-8</t>
+          <t>M-260105-7</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>M-260323-3</t>
+          <t>M-260323-2</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>M-260105-7</t>
+          <t>M-260105-6</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>M-260323-2</t>
+          <t>M-260323-1</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>M-260320-2</t>
+          <t>M-260320-1</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>M-260320-3</t>
+          <t>M-260320-2</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>M-260320-4</t>
+          <t>M-260320-3</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>M-260320-5</t>
+          <t>M-260320-4</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>M-251224-2</t>
+          <t>M-251224-1</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>M-260105-2</t>
+          <t>M-260105-1</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
